--- a/data/go_china.xlsx
+++ b/data/go_china.xlsx
@@ -1381,7 +1381,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trip.com App Homepage Banner</t>
+          <t>App Homepage Banner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trip.com App Hotel Homepage Banner</t>
+          <t>App Hotel Homepage Banner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trip.com App Flight Homepage Banner</t>
+          <t>App Flight Homepage Banner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
